--- a/pcb/JLCPCB_2layers_simplified/xiao_linefollower/production/lioncircuits/BOM_Lion.xlsx
+++ b/pcb/JLCPCB_2layers_simplified/xiao_linefollower/production/lioncircuits/BOM_Lion.xlsx
@@ -365,59 +365,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6A/16V PPTC</t>
+          <t xml:space="preserve">WALL_DL_LED wall-detection indicator (0603 green LED; firmware drives the PCF8574 pin LOW via I2C when this sensor's ADC reading crosses its wall-detected threshold)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MINISMDC260F/16-2</t>
+          <t xml:space="preserve">APT1608SGC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6A/16V PPTC</t>
+          <t xml:space="preserve">WALL_DL_LED wall-detection indicator</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuse_1812_4532Metric</t>
+          <t xml:space="preserve">LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">D50,D51,D52,D53,D54,D55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATT_IN_2S</t>
+          <t xml:space="preserve">2.6A/16V PPTC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2B-XH-A</t>
+          <t xml:space="preserve">MINISMDC260F/16-2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATT_IN_2S</t>
+          <t xml:space="preserve">2.6A/16V PPTC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
+          <t xml:space="preserve">Fuse_1812_4532Metric</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">J1</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -429,209 +429,209 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOTOR_A_N20_ENCODER</t>
+          <t xml:space="preserve">BATT_IN_2S</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6B-ZR(LF)(SN)</t>
+          <t xml:space="preserve">B2B-XH-A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOTOR_A_N20_ENCODER</t>
+          <t xml:space="preserve">BATT_IN_2S</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JST_ZH_B6B-ZR_1x06_P1.50mm_Vertical</t>
+          <t xml:space="preserve">JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">J5,J6</t>
+          <t xml:space="preserve">J1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATT_IN_XT60 (parallel option -- ONE PACK ONLY)</t>
+          <t xml:space="preserve">MOTOR_A_N20_ENCODER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">XT60-M</t>
+          <t xml:space="preserve">B6B-ZR(LF)(SN)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATT_IN_XT60</t>
+          <t xml:space="preserve">MOTOR_A_N20_ENCODER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMASS_XT60-M_1x02_P7.20mm_Vertical</t>
+          <t xml:space="preserve">JST_ZH_B6B-ZR_1x06_P1.50mm_Vertical</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">J10</t>
+          <t xml:space="preserve">J5,J6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7uH</t>
+          <t xml:space="preserve">BATT_IN_XT60 (parallel option -- ONE PACK ONLY)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRP4020TA-4R7M</t>
+          <t xml:space="preserve">XT60-M</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7uH</t>
+          <t xml:space="preserve">BATT_IN_XT60</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">L_Bourns_SRP4020TA</t>
+          <t xml:space="preserve">AMASS_XT60-M_1x02_P7.20mm_Vertical</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1,L2</t>
+          <t xml:space="preserve">J10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q_PMOS reverse guard (DMP3098L-7: Vgs +/-20V, 2S-safe)</t>
+          <t xml:space="preserve">4.7uH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DMP3098L-7</t>
+          <t xml:space="preserve">SRP4020TA-4R7M</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q_PMOS reverse guard</t>
+          <t xml:space="preserve">4.7uH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-23</t>
+          <t xml:space="preserve">L_Bourns_SRP4020TA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">L1,L2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT334-6B (5mm filtered PT; LONG LEAD = EMITTER; SFH309 base symbol so ERC checks pins)</t>
+          <t xml:space="preserve">Q_PMOS reverse guard (DMP3098L-7: Vgs +/-20V, 2S-safe)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT334-6B</t>
+          <t xml:space="preserve">DMP3098L-7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PT334-6B</t>
+          <t xml:space="preserve">Q_PMOS reverse guard</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED_D5.0mm_IRBlack</t>
+          <t xml:space="preserve">SOT-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2,Q3,Q4,Q5,Q6,Q7</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSS138 (real part; Q_NMOS_GSD base symbol used so ERC checks pins)</t>
+          <t xml:space="preserve">PT334-6B (5mm filtered PT; LONG LEAD = EMITTER; SFH309 base symbol so ERC checks pins)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSS138LT1G</t>
+          <t xml:space="preserve">PT334-6B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSS138</t>
+          <t xml:space="preserve">PT334-6B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-23</t>
+          <t xml:space="preserve">LED_D5.0mm_IRBlack</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q16,Q17,Q18</t>
+          <t xml:space="preserve">Q2,Q3,Q4,Q5,Q6,Q7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMBT2222A (buzzer low-side driver; Q_NPN_BEC base symbol so ERC checks pins)</t>
+          <t xml:space="preserve">BSS138 (real part; Q_NMOS_GSD base symbol used so ERC checks pins)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMBT2222A-7-F</t>
+          <t xml:space="preserve">BSS138LT1G</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMBT2222A</t>
+          <t xml:space="preserve">BSS138</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -641,93 +641,93 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q34</t>
+          <t xml:space="preserve">Q16,Q17,Q18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QRE1113GR (onsemi SMT reflective sensor; Pololu QTR sensor part; pin1=Anode pin2=Cathode(IR LED) pin3=Collector pin4=Emitter(phototransistor); B.Cu placement, faces the floor)</t>
+          <t xml:space="preserve">MMBT2222A (buzzer low-side driver; Q_NPN_BEC base symbol so ERC checks pins)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QRE1113GR</t>
+          <t xml:space="preserve">MMBT2222A-7-F</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QRE1113GR</t>
+          <t xml:space="preserve">MMBT2222A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QRE1113GR</t>
+          <t xml:space="preserve">SOT-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q41,Q42,Q43,Q44,Q45,Q46,Q47,Q48</t>
+          <t xml:space="preserve">Q34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100k</t>
+          <t xml:space="preserve">QRE1113GR (onsemi SMT reflective sensor; Pololu QTR sensor part; pin1=Anode pin2=Cathode(IR LED) pin3=Collector pin4=Emitter(phototransistor); B.Cu placement, faces the floor)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-07100KL</t>
+          <t xml:space="preserve">QRE1113GR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100k</t>
+          <t xml:space="preserve">QRE1113GR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">R_0805_2012Metric</t>
+          <t xml:space="preserve">QRE1113GR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1,R62,R63,R64,R69,R73</t>
+          <t xml:space="preserve">Q41,Q42,Q43,Q44,Q45,Q46,Q47,Q48</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10k</t>
+          <t xml:space="preserve">100k</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR08X1002FTL</t>
+          <t xml:space="preserve">RC0805FR-07100KL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">10k</t>
+          <t xml:space="preserve">100k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -737,29 +737,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">R6,R7,R8,R9,R55</t>
+          <t xml:space="preserve">R1,R62,R63,R64,R69,R73</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">47k</t>
+          <t xml:space="preserve">10k</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-0747KL</t>
+          <t xml:space="preserve">WR08X1002FTL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">47k</t>
+          <t xml:space="preserve">10k</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -769,29 +769,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">R13,R15,R17,R19,R21,R23</t>
+          <t xml:space="preserve">R6,R7,R8,R9,R55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">47k</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-0733RL</t>
+          <t xml:space="preserve">RC0805FR-0747KL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">47k</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">R14,R16,R18,R20,R22,R24</t>
+          <t xml:space="preserve">R13,R15,R17,R19,R21,R23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -813,17 +813,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">220k</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-07220KL</t>
+          <t xml:space="preserve">RC0805FR-0733RL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">220k</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -833,29 +833,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">R70</t>
+          <t xml:space="preserve">R14,R16,R18,R20,R22,R24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">110k</t>
+          <t xml:space="preserve">220k</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-07110KL</t>
+          <t xml:space="preserve">RC0805FR-07220KL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">110k</t>
+          <t xml:space="preserve">220k</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">R71</t>
+          <t xml:space="preserve">R70</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -877,17 +877,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11k</t>
+          <t xml:space="preserve">110k</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-0711KL</t>
+          <t xml:space="preserve">RC0805FR-07110KL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11k</t>
+          <t xml:space="preserve">110k</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">R74</t>
+          <t xml:space="preserve">R71</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">11k</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-07220RL</t>
+          <t xml:space="preserve">RC0805FR-0711KL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">11k</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -929,29 +929,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">R81,R91,R92,R93,R94,R95,R96,R97,R98</t>
+          <t xml:space="preserve">R74</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1k</t>
+          <t xml:space="preserve">220</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-071KL</t>
+          <t xml:space="preserve">RC0805FR-07220RL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1k</t>
+          <t xml:space="preserve">220</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -961,29 +961,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">R82,R84</t>
+          <t xml:space="preserve">R81,R91,R92,R93,R94,R95,R96,R97,R98,R105,R106,R107,R108,R109,R110</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.2k</t>
+          <t xml:space="preserve">1k</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-0740K2L</t>
+          <t xml:space="preserve">RC0805FR-071KL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.2k</t>
+          <t xml:space="preserve">1k</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -993,29 +993,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">R85</t>
+          <t xml:space="preserve">R82,R84</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2k</t>
+          <t xml:space="preserve">40.2k</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0805FR-072K2L</t>
+          <t xml:space="preserve">RC0805FR-0740K2L</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2k</t>
+          <t xml:space="preserve">40.2k</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1025,39 +1025,39 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">R103,R104</t>
+          <t xml:space="preserve">R85</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tactile pushbutton switch</t>
+          <t xml:space="preserve">2.2k</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">KMR221NGLFS</t>
+          <t xml:space="preserve">RC0805FR-072K2L</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tactile pushbutton switch</t>
+          <t xml:space="preserve">2.2k</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW_Push_1P1T_NO_CK_KMR2</t>
+          <t xml:space="preserve">R_0805_2012Metric</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW1,SW2</t>
+          <t xml:space="preserve">R103,R104</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1069,91 +1069,91 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PWR ALL (PCM12SMTR slide; slide-to-GND = OFF)</t>
+          <t xml:space="preserve">Tactile pushbutton switch</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCM12SMTR</t>
+          <t xml:space="preserve">KMR221NGLFS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PWR ALL</t>
+          <t xml:space="preserve">Tactile pushbutton switch</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW_SPDT_PCM12</t>
+          <t xml:space="preserve">SW_Push_1P1T_NO_CK_KMR2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW5,SW6,SW7</t>
+          <t xml:space="preserve">SW1,SW2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP63203WU-7 (fixed 3.3V 2A buck; AP63200WU base symbol so ERC checks pins)</t>
+          <t xml:space="preserve">PWR ALL (PCM12SMTR slide; slide-to-GND = OFF)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP63203WU-7</t>
+          <t xml:space="preserve">PCM12SMTR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AP63203WU-7</t>
+          <t xml:space="preserve">PWR ALL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSOT-23-6</t>
+          <t xml:space="preserve">SW_SPDT_PCM12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">U1</t>
+          <t xml:space="preserve">SW5,SW6,SW7</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB6612FNG</t>
+          <t xml:space="preserve">AP63203WU-7 (fixed 3.3V 2A buck; AP63200WU base symbol so ERC checks pins)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB6612FNG,C,8,EL</t>
+          <t xml:space="preserve">AP63203WU-7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB6612FNG</t>
+          <t xml:space="preserve">AP63203WU-7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SSOP-24_5.3x8.2mm_P0.65mm</t>
+          <t xml:space="preserve">TSOT-23-6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2</t>
+          <t xml:space="preserve">U1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1165,27 +1165,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeed XIAO nRF52840 Sense Plus (SKU 102010694): D0-D5 ADC-capable, D6-D10 + 9 Plus pads digital-only. Own onboard IMU/RGB LED/USB-C/reset button.</t>
+          <t xml:space="preserve">TB6612FNG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">102010694 (Seeed XIAO nRF52840 Sense Plus -- HAND-SOLDER, NOT part of turnkey SMT assembly)</t>
+          <t xml:space="preserve">TB6612FNG,C,8,EL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeed XIAO nRF52840 Sense Plus</t>
+          <t xml:space="preserve">TB6612FNG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">XIAO-nRF52840-Plus-SMD</t>
+          <t xml:space="preserve">SSOP-24_5.3x8.2mm_P0.65mm</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">U3</t>
+          <t xml:space="preserve">U2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1197,27 +1197,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADS7830IPWR (I2C 8-ch 8-bit ADC, TSSOP-16; A0=A1=GND -&gt; addr 0x48; internal 2.5V ref; single-ended mode, COM unused)</t>
+          <t xml:space="preserve">Seeed XIAO nRF52840 Sense Plus (SKU 102010694): D0-D5 ADC-capable, D6-D10 + 9 Plus pads digital-only. Own onboard IMU/RGB LED/USB-C/reset button.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADS7830IPWR</t>
+          <t xml:space="preserve">102010694 (Seeed XIAO nRF52840 Sense Plus -- HAND-SOLDER, NOT part of turnkey SMT assembly)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADS7830IPWR</t>
+          <t xml:space="preserve">Seeed XIAO nRF52840 Sense Plus</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t xml:space="preserve">XIAO-nRF52840-Plus-SMD</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">U4</t>
+          <t xml:space="preserve">U3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1229,27 +1229,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCF8574DWR (8-bit I2C GPIO expander, SOIC-16W; A0=A1=A2=GND -&gt; addr 0x20/0x21; TCA9534 base symbol so ERC checks pins -- see comment above)</t>
+          <t xml:space="preserve">ADS7830IPWR (I2C 8-ch 8-bit ADC, TSSOP-16; A0=A1=GND -&gt; addr 0x48; internal 2.5V ref; single-ended mode, COM unused)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCF8574DWR</t>
+          <t xml:space="preserve">ADS7830IPWR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCF8574DWR</t>
+          <t xml:space="preserve">ADS7830IPWR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOIC-16W_7.5x10.3mm_P1.27mm</t>
+          <t xml:space="preserve">TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">U5</t>
+          <t xml:space="preserve">U4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1261,30 +1261,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t xml:space="preserve">PCF8574DWR (8-bit I2C GPIO expander, SOIC-16W; A0=A1=A2=GND -&gt; addr 0x20/0x21; TCA9534 base symbol so ERC checks pins -- see comment above)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCF8574DWR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PCF8574DWR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOIC-16W_7.5x10.3mm_P1.27mm</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t xml:space="preserve">TPS54302DDCR (6.0V/3A motor buck; FB=100k/11k)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t xml:space="preserve">TPS54302DDCR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">TPS54302DDCR</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t xml:space="preserve">U7</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
